--- a/AAII_Financials/Quarterly/NMR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NMR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>NMR</t>
   </si>
@@ -656,491 +656,503 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="40" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45291</v>
       </c>
       <c r="K7" s="2">
         <v>45291</v>
       </c>
       <c r="L7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3630000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3483100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3627200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3023300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3373700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2825000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2942700</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2839200</v>
       </c>
       <c r="K8" s="3">
         <v>2839200</v>
       </c>
       <c r="L8" s="3">
+        <v>2839200</v>
+      </c>
+      <c r="M8" s="3">
         <v>2462200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2413200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2444300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5482900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3406000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2763200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2695000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2773800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2734100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2978000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1616300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3341500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3266700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4384800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3257500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4531800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5274200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4684200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4789200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4317900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4165500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3917700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4621400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4796900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4180000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4230100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3788500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3937300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3779600</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>908400</v>
+      </c>
+      <c r="E9" s="3">
         <v>718900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>706600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>700700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>712400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>617900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>619100</v>
-      </c>
-      <c r="J9" s="3">
-        <v>565700</v>
       </c>
       <c r="K9" s="3">
         <v>565700</v>
       </c>
       <c r="L9" s="3">
+        <v>565700</v>
+      </c>
+      <c r="M9" s="3">
         <v>588900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>582400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>631600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2687900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1377400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>747700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>432100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>362600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>435100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>381400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>410800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>394200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>392200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>454700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1165400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1480100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1750900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1643100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1894100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1857800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1537100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1445200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1203900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1121100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1002500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>968200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>692200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>667400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>701700</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2721500</v>
+      </c>
+      <c r="E10" s="3">
         <v>2764200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2920600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2322600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2661200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2207100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2323600</v>
-      </c>
-      <c r="J10" s="3">
-        <v>2273600</v>
       </c>
       <c r="K10" s="3">
         <v>2273600</v>
       </c>
       <c r="L10" s="3">
+        <v>2273600</v>
+      </c>
+      <c r="M10" s="3">
         <v>1873400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1830800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1812700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2795000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2028600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2015400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2262800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2411100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2299000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2596600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1205500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2947300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2874500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3930200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2092100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3051600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3523300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3041100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2895100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2460000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2628300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2472500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3417500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3675800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3177500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3261800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3096300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3269900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3077800</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1297,8 +1310,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1413,13 +1429,16 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>32200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1427,8 +1446,8 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
+      <c r="G14" s="3">
+        <v>12800</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1451,8 +1470,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1529,47 +1548,50 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>107300</v>
+      </c>
+      <c r="E15" s="3">
         <v>106000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>111300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>107200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>109400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>99200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>105500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>109100</v>
       </c>
       <c r="K15" s="3">
         <v>109100</v>
       </c>
       <c r="L15" s="3">
+        <v>109100</v>
+      </c>
+      <c r="M15" s="3">
         <v>100700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>103700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>124700</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1645,8 +1667,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,240 +1709,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2920600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2559800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2516200</v>
       </c>
-      <c r="F17" s="3">
-        <v>2370600</v>
-      </c>
       <c r="G17" s="3">
+        <v>2357800</v>
+      </c>
+      <c r="H17" s="3">
         <v>2445300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2185100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2333900</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2280900</v>
       </c>
       <c r="K17" s="3">
         <v>2280900</v>
       </c>
       <c r="L17" s="3">
+        <v>2280900</v>
+      </c>
+      <c r="M17" s="3">
         <v>2082400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2092900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2273600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4889600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3205100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2684100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2366100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2223500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2600900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2400800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2794000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2378900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2615200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2834000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3475300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3896900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4093400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3999000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4555100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5036800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4161100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3793600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4197200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3705300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3429300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3530000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3058400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3086200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3054300</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>709400</v>
+      </c>
+      <c r="E18" s="3">
         <v>923300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1110900</v>
       </c>
-      <c r="F18" s="3">
-        <v>652700</v>
-      </c>
       <c r="G18" s="3">
+        <v>665500</v>
+      </c>
+      <c r="H18" s="3">
         <v>928400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>639900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>608900</v>
-      </c>
-      <c r="J18" s="3">
-        <v>558400</v>
       </c>
       <c r="K18" s="3">
         <v>558400</v>
       </c>
       <c r="L18" s="3">
+        <v>558400</v>
+      </c>
+      <c r="M18" s="3">
         <v>379800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>320300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>170700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>593300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>200900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>79100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>328800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>550300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>133100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>577200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1177600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>962700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>651500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1550800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-217800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>634800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1180800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>685200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>234000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-719000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>124000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>424200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1091600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>750700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>700100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>730100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>851100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>725300</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1958,8 +1990,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1996,8 +2029,8 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -2074,124 +2107,130 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>816700</v>
+      </c>
+      <c r="E21" s="3">
         <v>1029300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1222200</v>
       </c>
-      <c r="F21" s="3">
-        <v>759900</v>
-      </c>
       <c r="G21" s="3">
+        <v>772700</v>
+      </c>
+      <c r="H21" s="3">
         <v>1037900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>739000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>714300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>667500</v>
       </c>
       <c r="K21" s="3">
         <v>667500</v>
       </c>
       <c r="L21" s="3">
+        <v>667500</v>
+      </c>
+      <c r="M21" s="3">
         <v>480500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>424000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>295400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>707500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>298500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>180500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>426000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>655500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>240800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>684900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1050900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1073500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>772300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1681700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-71900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>769700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1325300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>836400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>374000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-580900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>134500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>257800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>563300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1274700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>916600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>859000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>892300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1005800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>882400</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2228,8 +2267,8 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2306,240 +2345,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>677200</v>
+      </c>
+      <c r="E23" s="3">
         <v>923300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1110900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>652700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>928400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>639900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>608900</v>
-      </c>
-      <c r="J23" s="3">
-        <v>558400</v>
       </c>
       <c r="K23" s="3">
         <v>558400</v>
       </c>
       <c r="L23" s="3">
+        <v>558400</v>
+      </c>
+      <c r="M23" s="3">
         <v>379800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>320300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>170700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>593300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>200900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>79100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>328800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>550300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>133100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>577200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1177600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>962700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>651500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1550800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-217800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>634800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1180800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>685200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>234000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-719000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>124000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>424200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1091600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>750700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>700100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>730100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>851100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>725300</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>195600</v>
+      </c>
+      <c r="E24" s="3">
         <v>276000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>366000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>158700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>246400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>195800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>188300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>188500</v>
       </c>
       <c r="K24" s="3">
         <v>188500</v>
       </c>
       <c r="L24" s="3">
+        <v>188500</v>
+      </c>
+      <c r="M24" s="3">
         <v>141600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>141300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>106000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>125200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>94000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>76400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>133400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>127000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>93600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>209800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-91100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>226600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>114500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>320000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>110300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>94200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-109100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>164100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>198700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>185900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>90100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>63000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>217700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>279900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>266000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>175400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>173000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>223700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>174900</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2654,240 +2702,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>481600</v>
+      </c>
+      <c r="E26" s="3">
         <v>647300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>744900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>494000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>682000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>444100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>420600</v>
-      </c>
-      <c r="J26" s="3">
-        <v>369900</v>
       </c>
       <c r="K26" s="3">
         <v>369900</v>
       </c>
       <c r="L26" s="3">
+        <v>369900</v>
+      </c>
+      <c r="M26" s="3">
         <v>238200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>179000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>64700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>468200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>106800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>195500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>423300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>39500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>367400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1086500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>736100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>536900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1230900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-328000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>540700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1289900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>521100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>35300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-904900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-85800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>61000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>206500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>811700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>484700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>524700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>557100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>627400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>550400</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>465000</v>
+      </c>
+      <c r="E27" s="3">
         <v>622200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>724800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>480600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>686800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>428500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>375200</v>
-      </c>
-      <c r="J27" s="3">
-        <v>358600</v>
       </c>
       <c r="K27" s="3">
         <v>358600</v>
       </c>
       <c r="L27" s="3">
+        <v>358600</v>
+      </c>
+      <c r="M27" s="3">
         <v>235900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>161400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>55500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>475300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>107000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>205600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>414500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>23200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>356400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1101800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>721000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>526900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1215700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-303700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>519900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1273500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>511400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>8100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-899400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-104400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>47500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>205000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>795200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>468700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>514000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>543400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>624000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>542700</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3002,8 +3059,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3118,8 +3178,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3234,8 +3297,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3350,8 +3416,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3388,8 +3457,8 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -3466,124 +3535,130 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>465000</v>
+      </c>
+      <c r="E33" s="3">
         <v>622200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>724800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>480600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>686800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>428500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>375200</v>
-      </c>
-      <c r="J33" s="3">
-        <v>358600</v>
       </c>
       <c r="K33" s="3">
         <v>358600</v>
       </c>
       <c r="L33" s="3">
+        <v>358600</v>
+      </c>
+      <c r="M33" s="3">
         <v>235900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>161400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>55500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>475300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>107000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>205600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>414500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>23200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>356400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1101800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>721000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>526900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1215700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-303700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>519900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1273500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>511400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>8100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-899400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-104400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>47500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>205000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>795200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>468700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>514000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>543400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>624000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>542700</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3698,245 +3773,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>465000</v>
+      </c>
+      <c r="E35" s="3">
         <v>622200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>724800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>480600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>686800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>428500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>375200</v>
-      </c>
-      <c r="J35" s="3">
-        <v>358600</v>
       </c>
       <c r="K35" s="3">
         <v>358600</v>
       </c>
       <c r="L35" s="3">
+        <v>358600</v>
+      </c>
+      <c r="M35" s="3">
         <v>235900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>161400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>55500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>475300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>107000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>205600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>414500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>23200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>356400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1101800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>721000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>526900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1215700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-303700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>519900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1273500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>511400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>8100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-899400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-104400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>47500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>205000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>795200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>468700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>514000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>543400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>624000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>542700</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
-      </c>
-      <c r="J38" s="2">
-        <v>45291</v>
       </c>
       <c r="K38" s="2">
         <v>45291</v>
       </c>
       <c r="L38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3977,8 +4061,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4019,163 +4104,167 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>27035000</v>
+      </c>
+      <c r="E41" s="3">
         <v>39647300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>34539600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>29546100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33694000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23969000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>28027900</v>
-      </c>
-      <c r="J41" s="3">
-        <v>34238300</v>
       </c>
       <c r="K41" s="3">
         <v>34238300</v>
       </c>
       <c r="L41" s="3">
+        <v>34238300</v>
+      </c>
+      <c r="M41" s="3">
         <v>27483900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>28022700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>28741200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24110100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>23450000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>23434800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22019800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>22447200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>30129600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>26285500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>26879400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>26660700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>32196700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>30147400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>30846100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>31144600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>28544200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>26104600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>28603300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>26298100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>29451500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>24967100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>24137600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>23391900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>26130900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>22817800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>24344900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>25126000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>28604500</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>210173600</v>
+      </c>
+      <c r="E42" s="3">
         <v>220579000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>291383700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>219151100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>239661300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>279847900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>224865300</v>
-      </c>
-      <c r="J42" s="3">
-        <v>177733100</v>
       </c>
       <c r="K42" s="3">
         <v>177733100</v>
       </c>
       <c r="L42" s="3">
+        <v>177733100</v>
+      </c>
+      <c r="M42" s="3">
         <v>232868000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>224774100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>227649000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4251,124 +4340,130 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>60015800</v>
+      </c>
+      <c r="E43" s="3">
         <v>53891700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>51883400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>49742500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>47583900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>45649400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>45180100</v>
-      </c>
-      <c r="J43" s="3">
-        <v>158286100</v>
       </c>
       <c r="K43" s="3">
         <v>158286100</v>
       </c>
       <c r="L43" s="3">
+        <v>158286100</v>
+      </c>
+      <c r="M43" s="3">
         <v>40919700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>38686600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>39171300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12521100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11688900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11527500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9865500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8699400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8977000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>10740100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8850000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8601500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>10824700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>12676300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>19993100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8362800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>13216800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>15558500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>12856500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>14144200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>11842400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>10489900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>12784800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>13209600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>10887600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>14916300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>10835600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>10837200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>10715200</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4405,8 +4500,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4483,163 +4578,169 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>73231900</v>
+      </c>
+      <c r="E45" s="3">
         <v>73463700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3949900</v>
       </c>
-      <c r="F45" s="3">
-        <v>62349500</v>
-      </c>
       <c r="G45" s="3">
+        <v>62351300</v>
+      </c>
+      <c r="H45" s="3">
         <v>63535800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3614700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>49327100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>50745600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>56372600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>45777900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2221100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2449100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2861200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2832100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2102000</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W45" s="3">
         <v>2648500</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
+      <c r="X45" s="3">
+        <v>0</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3">
         <v>2520900</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG45" s="3">
         <v>2732900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2846500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2612200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2265600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2265400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2369600</v>
       </c>
-      <c r="AL45" s="3">
-        <v>0</v>
-      </c>
       <c r="AM45" s="3">
         <v>0</v>
       </c>
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>370456200</v>
+      </c>
+      <c r="E46" s="3">
         <v>387581700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>381756700</v>
       </c>
-      <c r="F46" s="3">
-        <v>360789200</v>
-      </c>
       <c r="G46" s="3">
+        <v>360791000</v>
+      </c>
+      <c r="H46" s="3">
         <v>384475100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>353081000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>347400300</v>
-      </c>
-      <c r="J46" s="3">
-        <v>370257600</v>
       </c>
       <c r="K46" s="3">
         <v>370257600</v>
       </c>
       <c r="L46" s="3">
+        <v>370257600</v>
+      </c>
+      <c r="M46" s="3">
         <v>352017200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>347856000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>341339300</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4715,356 +4816,368 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12542600</v>
+      </c>
+      <c r="E47" s="3">
         <v>11879600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9138600</v>
       </c>
-      <c r="F47" s="3">
-        <v>10254100</v>
-      </c>
       <c r="G47" s="3">
+        <v>10204300</v>
+      </c>
+      <c r="H47" s="3">
         <v>9469400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6619400</v>
       </c>
-      <c r="I47" s="3">
-        <v>8656800</v>
-      </c>
       <c r="J47" s="3">
-        <v>14852800</v>
+        <v>8611000</v>
       </c>
       <c r="K47" s="3">
         <v>14852800</v>
       </c>
       <c r="L47" s="3">
+        <v>14852800</v>
+      </c>
+      <c r="M47" s="3">
         <v>8793800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8644200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8890300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>304279500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>285811500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>286203300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>248381200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>271919600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>265310800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>262061500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>257082300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>283266700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>279877800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>299799300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>326147000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>371543800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>368146600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>338334900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>343365000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>376713200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>370429500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>343923200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>318365500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>355816600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>351818700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>354297200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>329430800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>329610500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>326460000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3420300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2988600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2876200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2914600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3101500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2805600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2967100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>3311500</v>
       </c>
       <c r="K48" s="3">
         <v>3311500</v>
       </c>
       <c r="L48" s="3">
+        <v>3311500</v>
+      </c>
+      <c r="M48" s="3">
         <v>3099000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3181800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3492800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3161900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2747700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2913900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2782500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2979400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3317000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3428900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3292900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3361600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3633000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3694400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3880900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4191500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4219700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4561900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3357400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3039000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3009400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3069500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3064400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2940600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3030100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3217100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3101800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3018300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2986600</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1983500</v>
+      </c>
+      <c r="E49" s="3">
         <v>513300</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>489800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>215500</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>253800</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>274000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>269100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>272300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>256400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>218600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>221900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>199200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>197900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>204800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>209600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>205900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>202600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>224900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>256100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>156700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>167300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>170200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>173100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>190200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>190600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>968800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>933200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>899100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>969900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>978300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>940300</v>
       </c>
-      <c r="AL49" s="3">
-        <v>0</v>
-      </c>
       <c r="AM49" s="3">
         <v>0</v>
       </c>
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5179,8 +5292,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5295,124 +5411,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5321900</v>
+      </c>
+      <c r="E52" s="3">
         <v>4744100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8936400</v>
       </c>
-      <c r="F52" s="3">
-        <v>4702300</v>
-      </c>
       <c r="G52" s="3">
+        <v>4750300</v>
+      </c>
+      <c r="H52" s="3">
         <v>3633500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8866000</v>
       </c>
-      <c r="I52" s="3">
-        <v>5159200</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
+      <c r="J52" s="3">
+        <v>5205000</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>2691500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2966100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5199800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>254100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>273400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>287400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>217300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>309500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2599300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2699400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>348600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2403200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3341200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5023800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3553800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3169300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>270700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2381700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2887600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2933000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>188200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>172000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>145900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>126600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>126900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>167700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2017500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2348700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1954000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5527,124 +5649,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>393987100</v>
+      </c>
+      <c r="E54" s="3">
         <v>407920200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>402707900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>379318400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>401068200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>371372000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>364597600</v>
-      </c>
-      <c r="J54" s="3">
-        <v>388422000</v>
       </c>
       <c r="K54" s="3">
         <v>388422000</v>
       </c>
       <c r="L54" s="3">
+        <v>388422000</v>
+      </c>
+      <c r="M54" s="3">
         <v>366996200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>363061500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>359364800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>349621200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>328774000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>329608100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>288256700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>310629500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>312528600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>307452000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>301441800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>326861200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>332511800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>354382200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>387638400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>421267700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>419772600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>389598700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>393716300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>425866900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>421397500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>389310800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>364709300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>402096000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>398715500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>402079200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>380097900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>381872200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>381032500</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5685,8 +5813,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5727,47 +5856,48 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>31639200</v>
+      </c>
+      <c r="E57" s="3">
         <v>32562200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28048100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27668700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>30235000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>26469100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>27330800</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M57" s="3">
         <v>26039900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27437500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>23767700</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
@@ -5843,279 +5973,288 @@
       <c r="AN57" s="3">
         <v>0</v>
       </c>
+      <c r="AO57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>137756200</v>
+      </c>
+      <c r="E58" s="3">
         <v>144997200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>127393200</v>
       </c>
-      <c r="F58" s="3">
-        <v>142903200</v>
-      </c>
       <c r="G58" s="3">
+        <v>142584400</v>
+      </c>
+      <c r="H58" s="3">
         <v>160777900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>134239300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>145483400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>153327700</v>
       </c>
       <c r="K58" s="3">
         <v>153327700</v>
       </c>
       <c r="L58" s="3">
+        <v>153327700</v>
+      </c>
+      <c r="M58" s="3">
         <v>154848200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>144213300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>141364700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>146749900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>135190100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>135952200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>115197500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>131570400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>127123700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>124136100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>123732000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>141977900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>148587700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>156494200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>176847700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>209150700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>205519700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>182105700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>177789600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>220543600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>206051600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>183780500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>164331000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>187236400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>186805600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>199073700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>170890000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>162470800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>175295900</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>66669200</v>
+      </c>
+      <c r="E59" s="3">
         <v>75108700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>92057300</v>
       </c>
-      <c r="F59" s="3">
-        <v>64196600</v>
-      </c>
       <c r="G59" s="3">
+        <v>63341400</v>
+      </c>
+      <c r="H59" s="3">
         <v>63782700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>78065600</v>
       </c>
-      <c r="I59" s="3">
-        <v>60372700</v>
-      </c>
       <c r="J59" s="3">
-        <v>127504300</v>
+        <v>59808700</v>
       </c>
       <c r="K59" s="3">
         <v>127504300</v>
       </c>
       <c r="L59" s="3">
+        <v>127504300</v>
+      </c>
+      <c r="M59" s="3">
         <v>63304700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>67598000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>64627700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>29770700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>29415500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>28108100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>25349600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>26475200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>27706300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>24734500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>29165900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>29132800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>25453700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>26819500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>33690500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>30112800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>29561500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>27983700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>29516000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>28128600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>32111200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>32826000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>28927900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>30890100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>31931300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>29333800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>32893800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>35479000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>35033000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>240470700</v>
+      </c>
+      <c r="E60" s="3">
         <v>255961600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>247498600</v>
       </c>
-      <c r="F60" s="3">
-        <v>238353400</v>
-      </c>
       <c r="G60" s="3">
+        <v>237274500</v>
+      </c>
+      <c r="H60" s="3">
         <v>258071800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>238774000</v>
       </c>
-      <c r="I60" s="3">
-        <v>236991800</v>
-      </c>
       <c r="J60" s="3">
-        <v>280832000</v>
+        <v>236427800</v>
       </c>
       <c r="K60" s="3">
         <v>280832000</v>
       </c>
       <c r="L60" s="3">
+        <v>280832000</v>
+      </c>
+      <c r="M60" s="3">
         <v>247436000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>242238800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>233367100</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6191,165 +6330,171 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100853800</v>
+      </c>
+      <c r="E61" s="3">
         <v>100954300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>98909300</v>
       </c>
-      <c r="F61" s="3">
-        <v>92779100</v>
-      </c>
       <c r="G61" s="3">
+        <v>93097900</v>
+      </c>
+      <c r="H61" s="3">
         <v>95092500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>84452000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>86179900</v>
-      </c>
-      <c r="J61" s="3">
-        <v>83749100</v>
       </c>
       <c r="K61" s="3">
         <v>83749100</v>
       </c>
       <c r="L61" s="3">
+        <v>83749100</v>
+      </c>
+      <c r="M61" s="3">
         <v>79897900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>79675700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>82201800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>69599200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>64403900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>64473300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>61475200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>61234800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>62697800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>59647700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>56542800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>57650600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>62848300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>66818100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>69622000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>72070900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>72735500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>72424500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>76476100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>73092300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>71479500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>66623600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>66737900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>69396100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>69208100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>67965800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>63823300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>67233700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>65656600</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>27496000</v>
+      </c>
+      <c r="E62" s="3">
         <v>25778900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>31424500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24272400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23488200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25995900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18626600</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>17084700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18006000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18836400</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -6423,8 +6568,11 @@
       <c r="AN62" s="3">
         <v>0</v>
       </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6539,8 +6687,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6655,8 +6806,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6771,124 +6925,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>369743200</v>
+      </c>
+      <c r="E66" s="3">
         <v>383535500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>377832300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>355404900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>377361000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>349221900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>341798200</v>
-      </c>
-      <c r="J66" s="3">
-        <v>364581100</v>
       </c>
       <c r="K66" s="3">
         <v>364581100</v>
       </c>
       <c r="L66" s="3">
+        <v>364581100</v>
+      </c>
+      <c r="M66" s="3">
         <v>344418600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>339920500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>335111100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>327335600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>308594300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>309014200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>268903700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>291339400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>292815900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>287318700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>282334700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>306383900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>311234200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>330673100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>364261300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>396660000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>394887200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>365208200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>368431800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>400728800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>395378300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>363884000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>339855400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>376406900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>373076200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>376342100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>355351400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>356972000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>357621300</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6929,8 +7089,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7045,8 +7206,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7161,8 +7325,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7277,8 +7444,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7393,124 +7563,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12666200</v>
+      </c>
+      <c r="E72" s="3">
         <v>13351700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13606600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12470100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12525700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10967700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11277100</v>
-      </c>
-      <c r="J72" s="3">
-        <v>12014000</v>
       </c>
       <c r="K72" s="3">
         <v>12014000</v>
       </c>
       <c r="L72" s="3">
+        <v>12014000</v>
+      </c>
+      <c r="M72" s="3">
         <v>10999600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11285900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12389600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11896500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10262600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10829700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10670400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>11117800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11231000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>11608100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>10874000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12716900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13832600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15091500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14496400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>15443100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>15056400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>14182000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>14288400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>14123000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15620600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>15481000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>15339900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>15480900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>15701300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>15519600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>14752900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>14557200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>13937700</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7625,8 +7801,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7741,8 +7920,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7857,124 +8039,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23319200</v>
+      </c>
+      <c r="E76" s="3">
         <v>23551000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24092800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23178100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23039700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21526900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22149300</v>
-      </c>
-      <c r="J76" s="3">
-        <v>23265300</v>
       </c>
       <c r="K76" s="3">
         <v>23265300</v>
       </c>
       <c r="L76" s="3">
+        <v>23265300</v>
+      </c>
+      <c r="M76" s="3">
         <v>22036700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22584900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23685200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22285700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20179800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20594000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19353000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19290100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19712800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>20133300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19107100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>20477300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>21277600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>23709200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>23377000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24607600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>24885400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>24390600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>25284500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>25138200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>26019200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>25426800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>24853900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>25689100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>25639400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>25737100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>24746600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>24900200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>23411100</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8089,245 +8277,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
-      </c>
-      <c r="J80" s="2">
-        <v>45291</v>
       </c>
       <c r="K80" s="2">
         <v>45291</v>
       </c>
       <c r="L80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>465000</v>
+      </c>
+      <c r="E81" s="3">
         <v>622200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>724800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>480600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>686800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>428500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>375200</v>
-      </c>
-      <c r="J81" s="3">
-        <v>358600</v>
       </c>
       <c r="K81" s="3">
         <v>358600</v>
       </c>
       <c r="L81" s="3">
+        <v>358600</v>
+      </c>
+      <c r="M81" s="3">
         <v>235900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>161400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>55500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>475300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>107000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>205600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>414500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>23200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>356400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1101800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>721000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>526900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1215700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-303700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>519900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1273500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>511400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>8100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-899400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-104400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>47500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>205000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>795200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>468700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>514000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>543400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>624000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>542700</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8368,8 +8565,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8379,113 +8577,116 @@
       <c r="E83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>109100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>100700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>103700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>112800</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3">
         <v>121900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>105800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>110700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>120500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>114100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>97700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>101400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>97200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>105200</v>
-      </c>
-      <c r="T83" s="3">
-        <v>107600</v>
       </c>
       <c r="U83" s="3">
         <v>107600</v>
       </c>
       <c r="V83" s="3">
+        <v>107600</v>
+      </c>
+      <c r="W83" s="3">
         <v>126800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>110800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>120800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>130800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>145800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>134800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>144500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>151100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>140000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>138100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>130200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>133700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>139100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>183100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>165900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>159000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>162300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>154700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>157100</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8600,8 +8801,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8716,8 +8920,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8832,8 +9039,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8948,8 +9158,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9064,8 +9277,11 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9087,101 +9303,104 @@
       <c r="I89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J89" s="3">
-        <v>4579100</v>
+      <c r="J89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K89" s="3">
         <v>4579100</v>
       </c>
       <c r="L89" s="3">
+        <v>4579100</v>
+      </c>
+      <c r="M89" s="3">
         <v>-790400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2159200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1912700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2053200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1556900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2803000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2885600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4888100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2281900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3962500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-10800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1141400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3444500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3248600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3834300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4114200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1429900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1129000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>764900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-5188600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1812200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-783500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>862300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-2070800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1759300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-4579900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1788200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-3430100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>14843100</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9222,8 +9441,9 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9245,101 +9465,104 @@
       <c r="I91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J91" s="3">
-        <v>-459300</v>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>-459300</v>
       </c>
       <c r="L91" s="3">
+        <v>-459300</v>
+      </c>
+      <c r="M91" s="3">
         <v>-208700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-149600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-199900</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-32547000</v>
       </c>
       <c r="P91" s="3">
         <v>-32547000</v>
       </c>
       <c r="Q91" s="3">
+        <v>-32547000</v>
+      </c>
+      <c r="R91" s="3">
         <v>-23422000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-38702000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-20786000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-12919000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-286100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-298400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-190500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-267500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-148900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-211600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-853800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-363700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-452800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1206300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-508500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-487000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-793300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-885200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-858900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-334800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-499000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-691700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-318800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-891900</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9454,8 +9677,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9570,8 +9796,11 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9593,101 +9822,104 @@
       <c r="I94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J94" s="3">
-        <v>-4602400</v>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K94" s="3">
         <v>-4602400</v>
       </c>
       <c r="L94" s="3">
+        <v>-4602400</v>
+      </c>
+      <c r="M94" s="3">
         <v>-2151600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-79600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2123300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>403300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-115700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>69900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-58700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-209600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-388500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>352400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-469200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-500700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-166100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>143200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-12900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-88400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1661600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>427800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1053600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-295600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>145300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>116400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-718200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-465100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>714700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-39200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-169700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>373200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>292300</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9728,8 +9960,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9751,101 +9984,104 @@
       <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>171100</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>249300</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-106600</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-284800</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-170100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-337800</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-448300</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-129600</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-441700</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-91000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-95800</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-339300</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-283700</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-350900</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-283900</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9960,8 +10196,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10076,8 +10315,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10192,8 +10434,11 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10215,101 +10460,104 @@
       <c r="I100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J100" s="3">
-        <v>2420800</v>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K100" s="3">
         <v>2420800</v>
       </c>
       <c r="L100" s="3">
+        <v>2420800</v>
+      </c>
+      <c r="M100" s="3">
         <v>2897100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1447100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3381800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>560600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2420400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2534600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2616200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>883800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2374100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1608100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>806200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2455700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1422100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1971900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4334400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1197500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1636800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1892200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2671400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>648200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2553800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1269400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>424500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-296200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>603900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>2641300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2227000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1942400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-5023500</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10319,113 +10567,116 @@
       <c r="E101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3">
         <v>-751700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>402700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>965000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>25100</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3">
         <v>-957900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>562400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1399400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>809000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-896900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>519200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1281700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>652400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>307200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>96100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-48600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>683000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-111500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-132300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-27600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-136900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>159300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-249900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-230600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>250900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>382900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-590600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>25100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>57200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>24700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-371000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>1045800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>18500</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10448,96 +10699,99 @@
         <v>0</v>
       </c>
       <c r="J102" s="3">
-        <v>1645800</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>1645800</v>
       </c>
       <c r="L102" s="3">
+        <v>1645800</v>
+      </c>
+      <c r="M102" s="3">
         <v>357700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1597600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3196300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1986300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1267000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1083300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>324200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3906700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4363700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2050600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1009200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4209400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4568100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1392300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>350200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2987600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1850600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-585200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2383100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-5066600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4762200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>985100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-22000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2807100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>3135100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1953100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-979600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-3953500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>10130400</v>
       </c>
     </row>
